--- a/artfynd/A 39915-2026 artfynd.xlsx
+++ b/artfynd/A 39915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582886</v>
       </c>
       <c r="B2" t="n">
-        <v>98209</v>
+        <v>98215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39915-2026 artfynd.xlsx
+++ b/artfynd/A 39915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582886</v>
       </c>
       <c r="B2" t="n">
-        <v>98215</v>
+        <v>98217</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39915-2026 artfynd.xlsx
+++ b/artfynd/A 39915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582886</v>
       </c>
       <c r="B2" t="n">
-        <v>98217</v>
+        <v>98218</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39915-2026 artfynd.xlsx
+++ b/artfynd/A 39915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582886</v>
       </c>
       <c r="B2" t="n">
-        <v>98218</v>
+        <v>98224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39915-2026 artfynd.xlsx
+++ b/artfynd/A 39915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582886</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39915-2026 artfynd.xlsx
+++ b/artfynd/A 39915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582886</v>
       </c>
       <c r="B2" t="n">
-        <v>98228</v>
+        <v>98230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 39915-2026 artfynd.xlsx
+++ b/artfynd/A 39915-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136582886</v>
       </c>
       <c r="B2" t="n">
-        <v>98230</v>
+        <v>98232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
